--- a/artfynd/A 821-2024 artfynd.xlsx
+++ b/artfynd/A 821-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 821-2024 artfynd.xlsx
+++ b/artfynd/A 821-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5729,6 +5729,950 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>115061664</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>570508</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6697128</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>115061647</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>570514</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6697101</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>115061654</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79433</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>570554</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6697154</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115061645</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>570632</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6697362</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>115061652</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79433</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>570590</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6697173</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>115061667</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>570493</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6697151</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>115061643</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91194</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>570692</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6697555</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>115061633</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5185</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>570449</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6697498</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>115061641</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>570260</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6697357</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 821-2024 artfynd.xlsx
+++ b/artfynd/A 821-2024 artfynd.xlsx
@@ -2270,7 +2270,7 @@
         <v>112567709</v>
       </c>
       <c r="B17" t="n">
-        <v>56623</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>112558113</v>
       </c>
       <c r="B35" t="n">
-        <v>56623</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>113256057</v>
       </c>
       <c r="B47" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södra Spjutbo (Södra Spjutbo), Dlr</t>
+          <t>Södra Spjutbo, Södra Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -5512,7 +5512,7 @@
         <v>113260745</v>
       </c>
       <c r="B48" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>113499119</v>
       </c>
       <c r="B49" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 821-2024 artfynd.xlsx
+++ b/artfynd/A 821-2024 artfynd.xlsx
@@ -2270,7 +2270,7 @@
         <v>112567709</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>112558113</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>113256057</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>113260745</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>113499119</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 821-2024 artfynd.xlsx
+++ b/artfynd/A 821-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107563990</v>
+        <v>115061664</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
+        <v>99909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,20 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fjärden, Dlr</t>
+          <t>Södra Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570508.898441341</v>
+        <v>570508</v>
       </c>
       <c r="R2" t="n">
-        <v>6697126.694527358</v>
+        <v>6697127</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -6157,10 +6146,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>115061664</v>
+        <v>115061641</v>
       </c>
       <c r="B54" t="n">
-        <v>99909</v>
+        <v>57414</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6169,25 +6158,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6197,10 +6186,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>570508</v>
+        <v>570260</v>
       </c>
       <c r="R54" t="n">
-        <v>6697127</v>
+        <v>6697357</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6259,10 +6248,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>115061641</v>
+        <v>115061667</v>
       </c>
       <c r="B55" t="n">
-        <v>57414</v>
+        <v>99909</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6271,25 +6260,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6299,10 +6288,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>570260</v>
+        <v>570493</v>
       </c>
       <c r="R55" t="n">
-        <v>6697357</v>
+        <v>6697151</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6361,10 +6350,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>115061667</v>
+        <v>115061643</v>
       </c>
       <c r="B56" t="n">
-        <v>99909</v>
+        <v>91263</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6377,21 +6366,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6401,10 +6390,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>570493</v>
+        <v>570692</v>
       </c>
       <c r="R56" t="n">
-        <v>6697151</v>
+        <v>6697555</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6463,10 +6452,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>115061643</v>
+        <v>115061647</v>
       </c>
       <c r="B57" t="n">
-        <v>91263</v>
+        <v>57281</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6475,38 +6464,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>570692</v>
+        <v>570515</v>
       </c>
       <c r="R57" t="n">
-        <v>6697555</v>
+        <v>6697100</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6562,116 +6559,6 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>115061647</v>
-      </c>
-      <c r="B58" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Södra Spjutbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>570515</v>
-      </c>
-      <c r="R58" t="n">
-        <v>6697100</v>
-      </c>
-      <c r="S58" t="n">
-        <v>15</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Hedemora</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Husby</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
